--- a/employee_information_forms/042_time_clock_correction_form_template--employee_information_forms.xlsx
+++ b/employee_information_forms/042_time_clock_correction_form_template--employee_information_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'clock_in_error',_'label':_'clock_in_error'}</t>
+          <t>clock_in_error</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'clock_in_error', 'label': 'clock_in_error'}</t>
+          <t>clock in error</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'clock_out_error',_'label':_'clock_out_error'}</t>
+          <t>clock_out_error</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'clock_out_error', 'label': 'clock_out_error'}</t>
+          <t>clock out error</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'late_start',_'label':_'late_start'}</t>
+          <t>late_start</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'late_start', 'label': 'late_start'}</t>
+          <t>late start</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'early_out',_'label':_'early_out'}</t>
+          <t>early_out</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'early_out', 'label': 'early_out'}</t>
+          <t>early out</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'no_clock_in',_'label':_'no_clock_in'}</t>
+          <t>no_clock_in</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'no_clock_in', 'label': 'no_clock_in'}</t>
+          <t>no clock in</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'no_clock_out',_'label':_'no_clock_out'}</t>
+          <t>no_clock_out</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'no_clock_out', 'label': 'no_clock_out'}</t>
+          <t>no clock out</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'unknown_shift',_'label':_'unknown_shift'}</t>
+          <t>unknown_shift</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'unknown_shift', 'label': 'unknown_shift'}</t>
+          <t>unknown shift</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'incorrect_shift',_'label':_'incorrect_shift'}</t>
+          <t>incorrect_shift</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'incorrect_shift', 'label': 'incorrect_shift'}</t>
+          <t>incorrect shift</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'incorrect_work_period',_'label':_'incorrect_work_period'}</t>
+          <t>incorrect_work_period</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'incorrect_work_period', 'label': 'incorrect_work_period'}</t>
+          <t>incorrect work period</t>
         </is>
       </c>
     </row>
